--- a/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-PRS-01_toplam_verimli_bakim_proseduru_ve_takip_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-PRS-01_toplam_verimli_bakim_proseduru_ve_takip_matrisi.xlsx
@@ -952,7 +952,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-PRS-01&amp;C&amp;"Arial,Regular"&amp;11Toplam Verimli Bakım Prosedürü ve Takip Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 13.05.2026 | Revizyon: 12.08.2026
+Revizyon nedeni: Bakım planı ve prosedürü kritiklik, güvenli müdahale, iş emri ve üretime teslim esaslarıyla düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1146,7 +1147,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-PRS-01&amp;C&amp;"Arial,Regular"&amp;11Toplam Verimli Bakım Prosedürü ve Takip Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 13.05.2026 | Revizyon: 12.08.2026
+Revizyon nedeni: Bakım planı ve prosedürü kritiklik, güvenli müdahale, iş emri ve üretime teslim esaslarıyla düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>